--- a/Laboratorio03/validacao/rotulos_avaliador_1.xlsx
+++ b/Laboratorio03/validacao/rotulos_avaliador_1.xlsx
@@ -442,9 +442,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -466,9 +464,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -490,9 +486,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -559,9 +553,21 @@
           <t>https://github.com/microsoft/pyright</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>type checker usado por linha de comando e como language server</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,9 +580,16 @@
           <t>https://github.com/kcp-dev/kcp</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,9 +602,21 @@
           <t>https://github.com/databendlabs/databend</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>releases principais também são nightlies automáticas</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -604,9 +629,21 @@
           <t>https://github.com/nrwl/nx</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ferramenta de build de monorepo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,9 +656,16 @@
           <t>https://github.com/YosysHQ/yosys</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -634,9 +678,16 @@
           <t>https://github.com/ColinIanKing/stress-ng</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -649,9 +700,21 @@
           <t>https://github.com/emanuele-f/PCAPdroid</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>app Android</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -664,9 +727,16 @@
           <t>https://github.com/kubernetes-sigs/controller-runtime</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -679,9 +749,16 @@
           <t>https://github.com/litestar-org/litestar</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -694,9 +771,16 @@
           <t>https://github.com/JetBrains/koog</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -709,9 +793,21 @@
           <t>https://github.com/Azure/Enterprise-Scale</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>templates e policies de arquitetura; releases agregam atualizações de conteúdo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -724,9 +820,21 @@
           <t>https://github.com/cloudflare/vinext</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>plugin do Vite</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -739,9 +847,21 @@
           <t>https://github.com/OthmanAdi/planning-with-files</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>skill para agentes de código, distribuída via npm e marketplace</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -754,9 +874,21 @@
           <t>https://github.com/microsoft/fast</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>cada release publica um pacote no npm</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -769,9 +901,16 @@
           <t>https://github.com/elastic/elasticsearch-ruby</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -784,9 +923,21 @@
           <t>https://github.com/PDFCraftTool/pdfcraft</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>builds automáticos identificados por commit</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -799,9 +950,21 @@
           <t>https://github.com/francescopace/espectre</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>firmware para ESP32</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -814,9 +977,16 @@
           <t>https://github.com/mozilla-ai/llamafile</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -829,9 +999,16 @@
           <t>https://github.com/smapiot/piral</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -844,9 +1021,16 @@
           <t>https://github.com/huynhsontung/Screenbox</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -859,9 +1043,16 @@
           <t>https://github.com/quay/quay</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -874,9 +1065,16 @@
           <t>https://github.com/tailwindlabs/tailwindcss</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +1087,21 @@
           <t>https://github.com/sivchari/kumo</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emulador de serviços AWS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -904,9 +1114,21 @@
           <t>https://github.com/GLips/Figma-Context-MCP</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>servidor MCP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -919,9 +1141,16 @@
           <t>https://github.com/invoke-ai/InvokeAI</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -934,9 +1163,16 @@
           <t>https://github.com/projectdiscovery/nuclei</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -949,9 +1185,16 @@
           <t>https://github.com/AssetRipper/AssetRipper</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -964,9 +1207,16 @@
           <t>https://github.com/alpinejs/alpine</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -979,9 +1229,16 @@
           <t>https://github.com/vapor/vapor</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -994,9 +1251,16 @@
           <t>https://github.com/cunarist/rinf</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1009,9 +1273,16 @@
           <t>https://github.com/hashicorp/consul-template</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1024,9 +1295,16 @@
           <t>https://github.com/vava-nessa/free-coding-models</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1039,9 +1317,21 @@
           <t>https://github.com/open-telemetry/opentelemetry-collector-contrib</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>componentes do collector; a distribuição binária sai de outro repositório</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1054,9 +1344,16 @@
           <t>https://github.com/OpenAPITools/openapi-generator</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1069,9 +1366,21 @@
           <t>https://github.com/DietrichGebert/ponytail</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>skill/plugin de prompts para agentes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1084,9 +1393,16 @@
           <t>https://github.com/usebruno/bruno</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1099,9 +1415,16 @@
           <t>https://github.com/ankitects/anki</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1114,9 +1437,16 @@
           <t>https://github.com/bpmn-io/bpmn-js</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1129,9 +1459,21 @@
           <t>https://github.com/FuelLabs/sway</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>compilador e toolchain da linguagem</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1144,9 +1486,16 @@
           <t>https://github.com/Viren070/AIOStreams</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1159,9 +1508,16 @@
           <t>https://github.com/callstack/repack</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1174,9 +1530,16 @@
           <t>https://github.com/apache/doris</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1189,9 +1552,16 @@
           <t>https://github.com/spatie/laravel-responsecache</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1204,9 +1574,16 @@
           <t>https://github.com/droidrun/mobilerun</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1219,9 +1596,16 @@
           <t>https://github.com/CherryHQ/cherry-studio</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1234,9 +1618,16 @@
           <t>https://github.com/modelcontextprotocol/kotlin-sdk</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1249,9 +1640,16 @@
           <t>https://github.com/valkey-io/valkey</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1264,9 +1662,16 @@
           <t>https://github.com/apollographql/apollo-client</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1279,9 +1684,16 @@
           <t>https://github.com/vuetifyjs/vuetify</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1294,9 +1706,16 @@
           <t>https://github.com/rilldata/rill</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1309,9 +1728,16 @@
           <t>https://github.com/posit-dev/great-tables</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1324,9 +1750,21 @@
           <t>https://github.com/vstorm-co/full-stack-ai-agent-template</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>gerador de projetos</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1339,9 +1777,16 @@
           <t>https://github.com/aaif-goose/goose</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1354,9 +1799,21 @@
           <t>https://github.com/awalol/DS5Dongle</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>firmware para Pico</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1369,9 +1826,16 @@
           <t>https://github.com/mock-server/mockserver-monorepo</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1384,9 +1848,16 @@
           <t>https://github.com/rmyndharis/OpenWA</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1399,9 +1870,21 @@
           <t>https://github.com/phpactor/phpactor</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>language server para PHP</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1414,9 +1897,21 @@
           <t>https://github.com/coredevices/PebbleOS</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>firmware; releases sem notas</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1429,9 +1924,16 @@
           <t>https://github.com/zeroclaw-labs/zeroclaw</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1444,9 +1946,16 @@
           <t>https://github.com/mozilla/rhino</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1604,8 +2113,16 @@
           <t>https://github.com/microsoft/pyright/compare/1.1.405...1.1.406</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>notas e commits dominados por "Fixed bug"; novas checagens são pontuais</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1633,8 +2150,16 @@
           <t>https://github.com/microsoft/pyright/compare/1.1.406...1.1.407</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>maioria correções (inclui regressão do --createstub); mudança do Python padrão é secundária</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1662,8 +2187,16 @@
           <t>https://github.com/microsoft/pyright/compare/1.1.410...1.1.411</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>quase só correções de narrowing/dataclass/release</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1691,8 +2224,16 @@
           <t>https://github.com/microsoft/pyright/compare/1.1.412...1.1.413</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>mesmo dia da 1.1.414; corrige pipeline de publicação e alias de TypeForm</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1720,8 +2261,16 @@
           <t>https://github.com/microsoft/pyright/compare/1.1.413...1.1.414</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>mistura correções com funcionalidade nova (typeserver no npm, metadata de assinatura)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1749,8 +2298,11 @@
           <t>https://github.com/kcp-dev/kcp/compare/v0.28.3...v0.29.0</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1778,8 +2330,11 @@
           <t>https://github.com/kcp-dev/kcp/compare/v0.29.0...v0.30.0</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1807,8 +2362,11 @@
           <t>https://github.com/kcp-dev/kcp/compare/v0.29.3...v0.31.0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1836,8 +2394,16 @@
           <t>https://github.com/kcp-dev/kcp/compare/v0.32.2...v0.31.4</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>patch de branch antigo: CVE do spdystream e cherry-picks de correção de segurança</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1865,8 +2431,16 @@
           <t>https://github.com/kcp-dev/kcp/compare/v0.32.3...v0.31.6</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>corrige regressão, mas destaca nova flag --header-file</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1894,8 +2468,11 @@
           <t>https://github.com/databendlabs/databend/compare/v1.2.820-nightly...v1.2.828-nightly</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1923,8 +2500,16 @@
           <t>https://github.com/databendlabs/databend/compare/v1.2.828-nightly...v1.2.833-nightly</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>notas curtas, mas commits desde a 828 trazem várias funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1952,8 +2537,11 @@
           <t>https://github.com/databendlabs/databend/compare/v1.2.861-nightly...v1.2.870-nightly</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1981,8 +2569,11 @@
           <t>https://github.com/databendlabs/databend/compare/v1.2.881-nightly...v1.2.883-nightly</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2010,8 +2601,11 @@
           <t>https://github.com/databendlabs/databend/compare/v1.2.883-nightly...v1.2.881</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2039,8 +2633,16 @@
           <t>https://github.com/nrwl/nx/compare/21.6.2...21.6.3</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>só seção de Fixes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2068,8 +2670,11 @@
           <t>https://github.com/nrwl/nx/compare/21.6.6...22.0.0</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2097,8 +2702,11 @@
           <t>https://github.com/nrwl/nx/compare/21.6.10...22.2.0</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2126,8 +2734,16 @@
           <t>https://github.com/nrwl/nx/compare/22.3.0...22.3.1</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>duas correções</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2155,8 +2771,16 @@
           <t>https://github.com/nrwl/nx/compare/23.1.0...23.1.1</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>72 itens em Fixes contra 2 em Features (um deles é exemplo)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2184,8 +2808,11 @@
           <t>https://github.com/YosysHQ/yosys/compare/v0.57...v0.58</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2213,8 +2840,11 @@
           <t>https://github.com/YosysHQ/yosys/compare/v0.61...v0.62</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2242,8 +2872,11 @@
           <t>https://github.com/YosysHQ/yosys/compare/v0.64...v0.65</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2271,8 +2904,11 @@
           <t>https://github.com/YosysHQ/yosys/compare/v0.65...v0.66</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2300,8 +2936,11 @@
           <t>https://github.com/YosysHQ/yosys/compare/v0.67...v0.68</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2329,8 +2968,11 @@
           <t>https://github.com/ColinIanKing/stress-ng/compare/V0.19.04...V0.19.05</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2358,8 +3000,11 @@
           <t>https://github.com/ColinIanKing/stress-ng/compare/V0.19.06...V0.20.00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2387,8 +3032,11 @@
           <t>https://github.com/ColinIanKing/stress-ng/compare/V0.21.00...V0.21.01</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2416,8 +3064,11 @@
           <t>https://github.com/ColinIanKing/stress-ng/compare/V0.21.04...V0.22.00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2445,8 +3096,16 @@
           <t>https://github.com/ColinIanKing/stress-ng/compare/V0.22.00...V0.22.01</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>novo stressor bpf junto com correções</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2474,8 +3133,11 @@
           <t>https://github.com/emanuele-f/PCAPdroid/compare/v1.8.8...v1.9.0</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2503,8 +3165,16 @@
           <t>https://github.com/emanuele-f/PCAPdroid/compare/v1.9.0...v1.9.1</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>correção de crashes; troca da lib zstd é secundária</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2532,8 +3202,11 @@
           <t>https://github.com/emanuele-f/PCAPdroid/compare/v1.9.1...v2.0.0</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2561,8 +3234,16 @@
           <t>https://github.com/emanuele-f/PCAPdroid/compare/v2.0.0...v2.0.1</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>notas são quase só correções (firewall, certificado mitm, crash)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2590,8 +3271,16 @@
           <t>https://github.com/emanuele-f/PCAPdroid/compare/v2.0.1...v2.0.2</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>correções de vazamento, OOM e crash</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2619,8 +3308,16 @@
           <t>https://github.com/kubernetes-sigs/controller-runtime/compare/v0.22.1...v0.22.2</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>backport de correções (panic, priorityqueue)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2648,8 +3345,16 @@
           <t>https://github.com/kubernetes-sigs/controller-runtime/compare/v0.22.5...v0.23.1</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>notas só com bugs (cache sync, panic, fakeclient)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2677,8 +3382,11 @@
           <t>https://github.com/kubernetes-sigs/controller-runtime/compare/v0.23.3...v0.24.0</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2706,8 +3414,16 @@
           <t>https://github.com/kubernetes-sigs/controller-runtime/compare/v0.24.0...v0.24.1</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>corrige regressão da v0.24.0</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2735,8 +3451,11 @@
           <t>https://github.com/kubernetes-sigs/controller-runtime/compare/v0.24.1...v0.25.0</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2764,8 +3483,16 @@
           <t>https://github.com/litestar-org/litestar/compare/v2.17.0...v2.18.0</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>15 itens em Bugfixes e 8 em Other changes, sem funcionalidade destacada</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2793,8 +3520,16 @@
           <t>https://github.com/litestar-org/litestar/compare/v2.18.0...v2.19.0</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>12 bugfixes contra 2 outras mudanças</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2822,8 +3557,16 @@
           <t>https://github.com/litestar-org/litestar/compare/v2.19.0...v2.20.0</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>commits trazem várias funcionalidades (otel exclude_spans, CLI, DTO)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2851,8 +3594,16 @@
           <t>https://github.com/litestar-org/litestar/compare/v2.21.1...v2.22.0</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>backports e depreciações além das correções</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2880,8 +3631,16 @@
           <t>https://github.com/litestar-org/litestar/compare/v2.23.0...v2.24.0</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>maioria correções de OpenAPI/compressão; depreciação sem funcionalidade nova</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2909,8 +3668,11 @@
           <t>https://github.com/JetBrains/koog/compare/0.4.2...0.5.0</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2938,8 +3700,16 @@
           <t>https://github.com/JetBrains/koog/compare/0.5.0...0.5.1</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>seção Improvements com novos modelos/clientes</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2967,8 +3737,11 @@
           <t>https://github.com/JetBrains/koog/compare/0.5.2...0.5.3</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2996,8 +3769,11 @@
           <t>https://github.com/JetBrains/koog/compare/0.5.4...0.6.0</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3025,8 +3801,11 @@
           <t>https://github.com/JetBrains/koog/compare/0.6.2...0.6.3</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3054,8 +3833,11 @@
           <t>https://github.com/Azure/Enterprise-Scale/compare/2025-09-17...2026-01-21</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3083,8 +3865,16 @@
           <t>https://github.com/Azure/Enterprise-Scale/compare/2026-01-21...2026-02-03</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>corrige valores Deny e guardrails quebrados da release de 2026-01-21</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3112,8 +3902,16 @@
           <t>https://github.com/Azure/Enterprise-Scale/compare/2026-02-03...2026-02-20</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>mistura correção de regiões com atualização e documentação</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3141,8 +3939,16 @@
           <t>https://github.com/Azure/Enterprise-Scale/compare/2026-04-14...2026-04-15</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>limpeza de definições obsoletas</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3170,8 +3976,16 @@
           <t>https://github.com/Azure/Enterprise-Scale/compare/2026-04-29...2026-08-07</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>única mudança funcional é correção de policy</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3199,8 +4013,11 @@
           <t>https://github.com/cloudflare/vinext/commits/v0.0.27</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3228,8 +4045,11 @@
           <t>https://github.com/cloudflare/vinext/compare/v0.0.38...v0.0.39</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3257,8 +4077,16 @@
           <t>https://github.com/cloudflare/vinext/compare/v0.0.48...v0.0.49</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>duas correções</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3286,8 +4114,11 @@
           <t>https://github.com/cloudflare/vinext/compare/vinext%401.0.0-beta.10...create-vinext-app%401.0.0-beta.3</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3315,8 +4146,11 @@
           <t>https://github.com/cloudflare/vinext/compare/%40vinext%2Fcloudflare%401.0.0-beta.11...vinext%401.0.0-beta.13</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3344,8 +4178,16 @@
           <t>https://github.com/OthmanAdi/planning-with-files/compare/v2.1.0...v2.1.1</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>corrige caminho de templates na instalação via marketplace</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3373,8 +4215,16 @@
           <t>https://github.com/OthmanAdi/planning-with-files/compare/v2.4.0...v2.4.1</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>corrige estrutura de pastas duplicada</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3402,8 +4252,16 @@
           <t>https://github.com/OthmanAdi/planning-with-files/compare/v2.26.1...v2.26.2</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>corrige parsing do YAML quebrado pelos hooks</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3431,8 +4289,16 @@
           <t>https://github.com/OthmanAdi/planning-with-files/compare/v3.1.1...v3.1.2</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>corrige comando session-catchup sem PLUGIN_ROOT</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3460,8 +4326,16 @@
           <t>https://github.com/OthmanAdi/planning-with-files/compare/v3.8.0...v3.8.1</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>corrige resolução do plano no Pi (#208)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3489,8 +4363,16 @@
           <t>https://github.com/microsoft/fast/commits/%40microsoft%2Ffast-html_v1.0.0-alpha.54</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>notas genéricas de nightly, sem commits para julgar</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3518,8 +4400,16 @@
           <t>https://github.com/microsoft/fast/compare/%40microsoft%2Ffast-html_v1.0.0-alpha.54...%40microsoft%2Ffast-test-harness_v0.3.1</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>notas genéricas de nightly e compare vazio; sem evidência de correção</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3547,8 +4437,16 @@
           <t>https://github.com/microsoft/fast/compare/%40microsoft%2Ffast-element_v3.0.0-rc.3...%40microsoft%2Ffast-test-harness_v0.4.1-fast-element-v3-rc-20260615</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>notas genéricas de nightly e compare vazio</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3576,8 +4474,16 @@
           <t>https://github.com/microsoft/fast/compare/%40microsoft%2Ffast-build_v0.9.0...%40microsoft%2Ffast-element_v3.0.0</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>versão major; notas genéricas</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3605,8 +4511,16 @@
           <t>https://github.com/microsoft/fast/compare/%40microsoft%2Ffast-router_v1.0.0-alpha.31...%40microsoft%2Ffast-test-harness_v0.4.0</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>notas genéricas de nightly e compare vazio</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3634,8 +4548,11 @@
           <t>https://github.com/elastic/elasticsearch-ruby/compare/v9.1.2...v9.2.0</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3663,8 +4580,16 @@
           <t>https://github.com/elastic/elasticsearch-ruby/compare/v9.2.0...v9.1.3</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>atualização da especificação da API com novos parâmetros</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3692,8 +4617,16 @@
           <t>https://github.com/elastic/elasticsearch-ruby/compare/v9.3.0...v9.2.1</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>uma correção no BulkHelper junto com atualização da especificação (novos endpoints nos commits)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3721,8 +4654,16 @@
           <t>https://github.com/elastic/elasticsearch-ruby/compare/v9.4.1...v9.2.3</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>única entrada é correção de NoMethodError</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3750,8 +4691,16 @@
           <t>https://github.com/elastic/elasticsearch-ruby/compare/v9.3.4...v9.4.3</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>única entrada é correção de conflito de header</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3779,8 +4728,16 @@
           <t>https://github.com/PDFCraftTool/pdfcraft/commits/v2026.01.27-970992e</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>primeira release; adiciona docker compose</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3808,8 +4765,16 @@
           <t>https://github.com/PDFCraftTool/pdfcraft/compare/v2026.02.12-010d156...v2026.02.12-c878acd</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>único commit corrige cache busting do LibreOffice</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3837,8 +4802,16 @@
           <t>https://github.com/PDFCraftTool/pdfcraft/compare/v2026.06.19-3936f55...v2026.06.22-2845344</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>dois commits de correção (arrastar ferramentas, 404)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3866,8 +4839,16 @@
           <t>https://github.com/PDFCraftTool/pdfcraft/compare/v2026.07.16-48f6cb0...v2026.07.27-c938a0d</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>commit único de correções (PDF criptografado, i18n, 404)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3895,8 +4876,16 @@
           <t>https://github.com/PDFCraftTool/pdfcraft/compare/v2026.07.27-c938a0d...v2026.07.31-0a84e60</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>nova funcionalidade de edição de texto</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3924,8 +4913,11 @@
           <t>https://github.com/francescopace/espectre/commits/1.2.0</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3953,8 +4945,11 @@
           <t>https://github.com/francescopace/espectre/compare/2.0.0...2.1.0</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3982,8 +4977,11 @@
           <t>https://github.com/francescopace/espectre/compare/2.4.0...2.5.0</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4011,8 +5009,16 @@
           <t>https://github.com/francescopace/espectre/compare/2.5.1...2.6.0</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>muitas correções, mas destaca suporte ao ESP32-C5</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4040,8 +5046,11 @@
           <t>https://github.com/francescopace/espectre/compare/2.6.0...2.7.0</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4069,8 +5078,11 @@
           <t>https://github.com/mozilla-ai/llamafile/compare/0.9.3...0.10.0</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4098,8 +5110,11 @@
           <t>https://github.com/mozilla-ai/llamafile/compare/0.10.0...0.10.1</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4127,8 +5142,16 @@
           <t>https://github.com/mozilla-ai/llamafile/compare/0.10.1...0.10.2</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>correções de CPU junto com probe de GPU e atualização do llama.cpp</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4156,8 +5179,11 @@
           <t>https://github.com/mozilla-ai/llamafile/compare/0.10.3...0.10.4</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4185,8 +5211,11 @@
           <t>https://github.com/mozilla-ai/llamafile/compare/0.10.4...0.10.5</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4214,8 +5243,16 @@
           <t>https://github.com/smapiot/piral/compare/v1.9.0...v1.9.1</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2 correções contra melhoria no CLI e nova opção vite7</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4243,8 +5280,16 @@
           <t>https://github.com/smapiot/piral/compare/v1.10.2...v1.10.3</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>correções no piral-ng e atualizações de segurança; opção vite8 é secundária</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4272,8 +5317,16 @@
           <t>https://github.com/smapiot/piral/compare/v1.11.1...v1.11.2</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>corrige race condition e bug no webpack5; suporte declarado ao Angular 22 é secundário</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4301,8 +5354,16 @@
           <t>https://github.com/smapiot/piral/compare/v1.11.2...v1.12.1</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>atualização de dependências e novo conversor gea</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4330,8 +5391,16 @@
           <t>https://github.com/smapiot/piral/compare/v1.12.2...v1.12.3</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>correções junto com melhorias de Module Federation e react-router v8</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4359,8 +5428,11 @@
           <t>https://github.com/huynhsontung/Screenbox/compare/v0.16.0...v0.17.0</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4388,8 +5460,16 @@
           <t>https://github.com/huynhsontung/Screenbox/compare/v0.18.0...v0.18.1</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>notas dizem que a release corrige regressões</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4417,8 +5497,11 @@
           <t>https://github.com/huynhsontung/Screenbox/compare/v0.18.3...v0.19.0</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4446,8 +5529,11 @@
           <t>https://github.com/huynhsontung/Screenbox/compare/v0.20.1...v0.21.0</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4475,8 +5561,11 @@
           <t>https://github.com/huynhsontung/Screenbox/compare/v0.21.0...v0.22.0</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4504,8 +5593,16 @@
           <t>https://github.com/quay/quay/compare/v3.9.16...v3.13.9</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>patch de manutenção só com atualizações de segurança de dependências</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4533,8 +5630,16 @@
           <t>https://github.com/quay/quay/compare/v3.9.17...v3.13.10</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>patch só com atualização de segurança do Authlib</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4562,8 +5667,16 @@
           <t>https://github.com/quay/quay/compare/v3.9.18...v3.14.6</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>backport longo com funcionalidades de UI além de atualizações de dependências</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4591,8 +5704,16 @@
           <t>https://github.com/quay/quay/compare/v3.16.4...v3.14.8</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>correções de CVE e de config-tool</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4620,8 +5741,16 @@
           <t>https://github.com/quay/quay/compare/v3.10.22...v3.9.22</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>correções de segurança (RCE via pickle, node-forge) e dependências</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4649,8 +5778,16 @@
           <t>https://github.com/tailwindlabs/tailwindcss/compare/v4.1.13...v3.4.18</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>só seção Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4678,8 +5815,16 @@
           <t>https://github.com/tailwindlabs/tailwindcss/compare/v3.4.18...v4.1.14</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>17 itens, todos em Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4707,8 +5852,16 @@
           <t>https://github.com/tailwindlabs/tailwindcss/compare/v4.1.17...v3.4.19</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>uma correção</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4736,8 +5889,16 @@
           <t>https://github.com/tailwindlabs/tailwindcss/compare/v4.3.0...v4.3.1</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>22 itens em Fixed contra 1 em Added (flag --silent)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4765,8 +5926,16 @@
           <t>https://github.com/tailwindlabs/tailwindcss/compare/v4.3.1...v4.3.2</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>13 itens, todos em Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4794,8 +5963,16 @@
           <t>https://github.com/sivchari/kumo/compare/v0.5.2...v0.5.3</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>corrige token do goreleaser que quebrou a publicação</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4823,8 +6000,11 @@
           <t>https://github.com/sivchari/kumo/compare/v0.10.0...v0.11.0</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4852,8 +6032,16 @@
           <t>https://github.com/sivchari/kumo/compare/v0.25.0...v0.25.1</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>corrige invocação assíncrona do lambda e parsing do govulncheck</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4881,8 +6069,16 @@
           <t>https://github.com/sivchari/kumo/compare/v0.26.0...v0.27.0</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>muitas correções, mas adiciona emulação do Amazon Managed Prometheus</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4910,8 +6106,11 @@
           <t>https://github.com/sivchari/kumo/compare/v0.27.0...v0.28.0</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4939,8 +6138,16 @@
           <t>https://github.com/GLips/Figma-Context-MCP/compare/v0.6.3...v0.6.4</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>melhoria no tratamento de SVG, não correção</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4968,8 +6175,11 @@
           <t>https://github.com/GLips/Figma-Context-MCP/compare/v0.7.1...v0.8.0</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4997,8 +6207,16 @@
           <t>https://github.com/GLips/Figma-Context-MCP/compare/v0.10.0...v0.10.1</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>duas correções de mensagens de erro</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5026,8 +6244,11 @@
           <t>https://github.com/GLips/Figma-Context-MCP/compare/v0.11.0...v0.12.0</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5055,8 +6276,16 @@
           <t>https://github.com/GLips/Figma-Context-MCP/compare/v0.13.0...v0.13.1</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>refinamento da redução de payload da v0.13.0</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5084,8 +6313,11 @@
           <t>https://github.com/invoke-ai/InvokeAI/compare/v6.7.0...v6.8.0</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5113,8 +6345,16 @@
           <t>https://github.com/invoke-ai/InvokeAI/compare/v6.11.0...v6.11.1</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>notas se declaram bugfix release</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5142,8 +6382,16 @@
           <t>https://github.com/invoke-ai/InvokeAI/compare/v6.13.5...v6.13.6</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>corrige bug introduzido na v6.13.5</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5171,8 +6419,16 @@
           <t>https://github.com/invoke-ai/InvokeAI/compare/v6.13.7...v6.13.8</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>patch de segurança</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5200,8 +6456,16 @@
           <t>https://github.com/invoke-ai/InvokeAI/compare/v6.14.0...v6.14.1</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>4 correções contra seção de 3 funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5229,8 +6493,11 @@
           <t>https://github.com/projectdiscovery/nuclei/compare/v3.4.10...v3.5.0</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5258,8 +6525,11 @@
           <t>https://github.com/projectdiscovery/nuclei/compare/v3.6.2...v3.7.0</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5287,8 +6557,11 @@
           <t>https://github.com/projectdiscovery/nuclei/compare/v3.8.0...v3.9.0</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5316,8 +6589,16 @@
           <t>https://github.com/projectdiscovery/nuclei/compare/v3.9.0...v3.10.0</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>10 correções de segurança e 13 de bugs contra 1 funcionalidade</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5345,8 +6626,16 @@
           <t>https://github.com/projectdiscovery/nuclei/compare/v3.10.0...v3.11.0</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>mudança de comportamento: exige assinatura em templates JavaScript</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5374,8 +6663,11 @@
           <t>https://github.com/AssetRipper/AssetRipper/compare/1.3.4...1.3.5</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5403,8 +6695,16 @@
           <t>https://github.com/AssetRipper/AssetRipper/compare/1.3.5...1.3.6</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>mistura correções com remoção de recurso e nova página de UI</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5432,8 +6732,16 @@
           <t>https://github.com/AssetRipper/AssetRipper/compare/1.3.9...1.3.10</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>atualização de dependências e melhorias</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5461,8 +6769,16 @@
           <t>https://github.com/AssetRipper/AssetRipper/compare/1.3.11...1.3.12</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>refatoração do SerializedFile</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5490,8 +6806,16 @@
           <t>https://github.com/AssetRipper/AssetRipper/compare/1.3.12...1.3.14</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>suporte a novas versões do Unity e dependências</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5519,8 +6843,11 @@
           <t>https://github.com/alpinejs/alpine/compare/v3.15.0...v3.15.1</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5548,8 +6875,11 @@
           <t>https://github.com/alpinejs/alpine/compare/v3.15.1...v3.15.2</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5577,8 +6907,11 @@
           <t>https://github.com/alpinejs/alpine/compare/v3.15.8...v3.15.9</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5606,8 +6939,16 @@
           <t>https://github.com/alpinejs/alpine/compare/v3.16.2...v3.16.3</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>única mudança de código é a correção do x-mask</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5635,8 +6976,16 @@
           <t>https://github.com/alpinejs/alpine/compare/v3.17.0...v3.17.1</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>adiciona dwell timing ao plugin intersect</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5664,8 +7013,16 @@
           <t>https://github.com/vapor/vapor/compare/4.117.0...4.117.1</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>novo media type HEIC</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5693,8 +7050,16 @@
           <t>https://github.com/vapor/vapor/compare/4.117.1...4.117.2</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>só corrige documentação de código</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5722,8 +7087,16 @@
           <t>https://github.com/vapor/vapor/compare/4.119.1...4.119.2</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>corrige falha de build em paralelo</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5751,8 +7124,16 @@
           <t>https://github.com/vapor/vapor/compare/4.121.3...4.121.4</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>corrige bug de compressão de resposta</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5780,8 +7161,16 @@
           <t>https://github.com/vapor/vapor/compare/5.0.0-beta.1...5.0.0-beta.2</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>corrige resolução de dependências do SwiftPM na beta 1</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5809,8 +7198,16 @@
           <t>https://github.com/cunarist/rinf/compare/v8.7.2...v8.8.0</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>suporte a Windows ARM64</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5838,8 +7235,16 @@
           <t>https://github.com/cunarist/rinf/compare/v8.8.0...v8.8.1</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>resumo da release: corrige compilação web quebrada</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5867,8 +7272,11 @@
           <t>https://github.com/cunarist/rinf/compare/v8.8.1...v8.9.0</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5896,8 +7304,11 @@
           <t>https://github.com/cunarist/rinf/compare/v8.9.1...v8.10.0</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5925,8 +7336,16 @@
           <t>https://github.com/cunarist/rinf/compare/v8.10.0...v8.10.1</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>manutenção de tooling e documentação</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5954,8 +7373,16 @@
           <t>https://github.com/hashicorp/consul-template/compare/v0.41.2...v0.41.3</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>correção de vulnerabilidade (SECVULN-14566) e Go atualizado por CVE</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5983,8 +7410,16 @@
           <t>https://github.com/hashicorp/consul-template/compare/v0.41.3...v0.41.4</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>nova função importedServices</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6012,8 +7447,16 @@
           <t>https://github.com/hashicorp/consul-template/compare/v0.41.4...v0.42.0</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>CVE de symlink e dois bugs; demais itens são atualizações</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6041,8 +7484,16 @@
           <t>https://github.com/hashicorp/consul-template/compare/v0.42.0...v0.42.1</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>correção de CVE no writeToFile</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6070,8 +7521,16 @@
           <t>https://github.com/hashicorp/consul-template/compare/v0.42.1...v0.43.0</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>notas vazias; commits são quase só correções de segurança e bugs, com um campo novo de TLS</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6099,8 +7558,16 @@
           <t>https://github.com/vava-nessa/free-coding-models/compare/v0.1.42...v0.1.43</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>patch intermediário sem conteúdo descrito; commit só de versão</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6128,8 +7595,11 @@
           <t>https://github.com/vava-nessa/free-coding-models/compare/v0.5.12...v0.5.15</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6157,8 +7627,16 @@
           <t>https://github.com/vava-nessa/free-coding-models/compare/v0.5.18...v0.5.19</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>adiciona modelos além de corrigir janelas de contexto</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6186,8 +7664,16 @@
           <t>https://github.com/vava-nessa/free-coding-models/compare/v0.5.45...v0.5.46</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>corrige catálogo do LLM7</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6215,8 +7701,11 @@
           <t>https://github.com/vava-nessa/free-coding-models/compare/v0.5.58...v0.5.59</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6244,8 +7733,11 @@
           <t>https://github.com/open-telemetry/opentelemetry-collector-contrib/compare/v0.136.0...v0.137.0</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6273,8 +7765,11 @@
           <t>https://github.com/open-telemetry/opentelemetry-collector-contrib/compare/v0.144.0...v0.145.0</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6302,8 +7797,11 @@
           <t>https://github.com/open-telemetry/opentelemetry-collector-contrib/compare/v0.147.0...v0.148.0</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6331,8 +7829,11 @@
           <t>https://github.com/open-telemetry/opentelemetry-collector-contrib/compare/v0.152.0...v0.153.0</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6360,8 +7861,11 @@
           <t>https://github.com/open-telemetry/opentelemetry-collector-contrib/compare/v0.160.0...v0.161.0</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6389,8 +7893,11 @@
           <t>https://github.com/OpenAPITools/openapi-generator/compare/v7.16.0...v7.17.0</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6418,8 +7925,11 @@
           <t>https://github.com/OpenAPITools/openapi-generator/compare/v7.17.0...v7.18.0</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6447,8 +7957,11 @@
           <t>https://github.com/OpenAPITools/openapi-generator/compare/v7.21.0...v7.22.0</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6476,8 +7989,11 @@
           <t>https://github.com/OpenAPITools/openapi-generator/compare/v7.23.0...v7.24.0</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6505,8 +8021,11 @@
           <t>https://github.com/OpenAPITools/openapi-generator/compare/v7.24.0...v7.25.0</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6534,8 +8053,11 @@
           <t>https://github.com/DietrichGebert/ponytail/commits/v1.0.0</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6563,8 +8085,11 @@
           <t>https://github.com/DietrichGebert/ponytail/compare/v1.0.0...v4.0.0</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6592,8 +8117,11 @@
           <t>https://github.com/DietrichGebert/ponytail/compare/v4.3.0...v4.4.0</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6621,8 +8149,11 @@
           <t>https://github.com/DietrichGebert/ponytail/compare/v4.8.3...v4.8.4</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6650,8 +8181,16 @@
           <t>https://github.com/DietrichGebert/ponytail/compare/v4.8.4...v4.9.0</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>cerca de 30 correções, mas a release destaca funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6679,8 +8218,11 @@
           <t>https://github.com/usebruno/bruno/compare/v2.15.1...v3.0.0</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6708,8 +8250,16 @@
           <t>https://github.com/usebruno/bruno/compare/v3.1.0...v3.1.1</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>só seção Fixes</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6737,8 +8287,11 @@
           <t>https://github.com/usebruno/bruno/compare/v3.1.4...v3.2.0</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6766,8 +8319,11 @@
           <t>https://github.com/usebruno/bruno/compare/v3.4.2...v3.5.0</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6795,8 +8351,11 @@
           <t>https://github.com/usebruno/bruno/compare/v4.1.0...v4.2.0</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6824,8 +8383,16 @@
           <t>https://github.com/ankitects/anki/compare/25.09.1...25.09.3</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>release de segurança (servidor de mídia local)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6853,8 +8420,16 @@
           <t>https://github.com/ankitects/anki/compare/25.09.3...25.09.4</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>release de segurança (importação de decks)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6882,8 +8457,11 @@
           <t>https://github.com/ankitects/anki/compare/25.09.4...26.05</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6911,8 +8489,16 @@
           <t>https://github.com/ankitects/anki/compare/26.08.1...26.09</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>traz correções de segurança, mas também novo instalador/remoção de módulos e mudanças notáveis</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6940,8 +8526,16 @@
           <t>https://github.com/ankitects/anki/compare/26.09.2...26.09.3</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>só seção Fixes</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6969,8 +8563,16 @@
           <t>https://github.com/bpmn-io/bpmn-js/compare/v18.15.0...v18.16.0</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>labels redimensionáveis</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6998,8 +8600,11 @@
           <t>https://github.com/bpmn-io/bpmn-js/compare/v18.16.1...v18.17.0</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7027,8 +8632,11 @@
           <t>https://github.com/bpmn-io/bpmn-js/compare/v18.21.0...v18.22.0</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7056,8 +8664,16 @@
           <t>https://github.com/bpmn-io/bpmn-js/compare/v18.23.0...v18.24.0</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>só atualização de dependência</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7085,8 +8701,16 @@
           <t>https://github.com/bpmn-io/bpmn-js/compare/v18.25.0...v18.25.1</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>correções de acessibilidade e foco no drilldown</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7114,8 +8738,16 @@
           <t>https://github.com/FuelLabs/sway/compare/v0.69.6...v0.70.0</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>correções misturadas com telemetria e estabilização de new_hashing</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7143,8 +8775,16 @@
           <t>https://github.com/FuelLabs/sway/compare/v0.70.0...v0.70.1</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>reverte telemetria, mas também traz backtracing e atualização do fuel-core</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7172,8 +8812,11 @@
           <t>https://github.com/FuelLabs/sway/compare/v0.71.0...v0.71.1</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7201,8 +8844,11 @@
           <t>https://github.com/FuelLabs/sway/compare/v0.71.2...v0.72.0</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7230,8 +8876,16 @@
           <t>https://github.com/FuelLabs/sway/compare/v0.72.0...v0.72.1</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>refatorações e otimizações com duas correções</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7259,8 +8913,16 @@
           <t>https://github.com/Viren070/AIOStreams/compare/v2.21.2...v2.21.3</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>uma correção no preset sootio</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7288,8 +8950,11 @@
           <t>https://github.com/Viren070/AIOStreams/compare/v2.25.1...v2.25.2</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7317,8 +8982,11 @@
           <t>https://github.com/Viren070/AIOStreams/compare/v2.27.2...seanime-extension-v0.7.0</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7346,8 +9014,16 @@
           <t>https://github.com/Viren070/AIOStreams/compare/seanime-extensions-v0.8.2...v2.29.5</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>uma correção no parser de HDR</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7375,8 +9051,16 @@
           <t>https://github.com/Viren070/AIOStreams/compare/v2.29.5...v2.29.6</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3 correções contra 1 função nova pequena (keyword)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7404,8 +9088,16 @@
           <t>https://github.com/callstack/repack/compare/%40callstack%2Frepack%405.2.1...%40callstack%2Frepack%405.2.2</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>corrige erro ESM no Windows</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7433,8 +9125,16 @@
           <t>https://github.com/callstack/repack/compare/%40callstack%2Frepack%405.2.2...%40callstack%2Frepack%405.2.3</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>corrige problema com nativewind</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7462,8 +9162,16 @@
           <t>https://github.com/callstack/repack/compare/%40callstack%2Frepack%405.2.3...%40callstack%2Frepack%405.2.4</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>várias correções e CVE do Fastify</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7491,8 +9199,11 @@
           <t>https://github.com/callstack/repack/compare/%40callstack%2Frepack%405.2.5...%40callstack%2Frepack%405.3.0</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7520,8 +9231,11 @@
           <t>https://github.com/callstack/repack/compare/%40callstack%2Frepack%405.3.0...%40callstack%2Frepack%405.4.0</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7549,8 +9263,11 @@
           <t>https://github.com/apache/doris/compare/3.1.1-rc01...4.0.0-rc02</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7578,8 +9295,16 @@
           <t>https://github.com/apache/doris/compare/4.0.0-rc02...3.1.2-rc01</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>notas só apontam para o changelog externo; compare inclui todo o histórico, sem evidência clara</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7607,8 +9332,16 @@
           <t>https://github.com/apache/doris/compare/4.0.1-rc02...3.1.3-rc02</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>notas só apontam para o changelog externo; sem evidência clara</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7636,8 +9369,16 @@
           <t>https://github.com/apache/doris/compare/4.0.2-rc02...3.1.4-rc02</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>notas só apontam para o changelog externo; sem evidência clara</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7665,8 +9406,16 @@
           <t>https://github.com/apache/doris/compare/4.0.4-release...4.0.5</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>commits misturam correções com melhorias e funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7694,8 +9443,11 @@
           <t>https://github.com/spatie/laravel-responsecache/compare/7.7.2...8.0.0</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7723,8 +9475,16 @@
           <t>https://github.com/spatie/laravel-responsecache/compare/8.1.0...8.2.0</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>suporte a Laravel 13 e PHP 8.5</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7752,8 +9512,16 @@
           <t>https://github.com/spatie/laravel-responsecache/compare/8.3.1...8.4.0</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>única mudança de código corrige race condition em has/get</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7781,8 +9549,16 @@
           <t>https://github.com/spatie/laravel-responsecache/compare/8.4.3...8.4.4</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>corrige cache de resposta não aprovada; resto é teste</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7810,8 +9586,16 @@
           <t>https://github.com/spatie/laravel-responsecache/compare/8.4.4...8.4.5</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>só atualização de dependência de teste</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7839,8 +9623,16 @@
           <t>https://github.com/droidrun/mobilerun/compare/v0.4.12...v0.4.13</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>corrige caminho do IME</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7868,8 +9660,11 @@
           <t>https://github.com/droidrun/mobilerun/compare/v0.4.25...v0.4.26</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7897,8 +9692,11 @@
           <t>https://github.com/droidrun/mobilerun/compare/v0.6.9...v0.6.10</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7926,8 +9724,16 @@
           <t>https://github.com/droidrun/mobilerun/compare/v0.6.12...v0.6.13</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>três correções</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7955,8 +9761,16 @@
           <t>https://github.com/droidrun/mobilerun/compare/v0.6.15...v0.6.16</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>suporte a Grok</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7984,8 +9798,11 @@
           <t>https://github.com/CherryHQ/cherry-studio/compare/v1.6.2...v1.6.3</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8013,8 +9830,11 @@
           <t>https://github.com/CherryHQ/cherry-studio/compare/v1.6.7...v1.7.0</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8042,8 +9862,16 @@
           <t>https://github.com/CherryHQ/cherry-studio/compare/v1.7.7...v1.7.8</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>quase só correções</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8071,8 +9899,16 @@
           <t>https://github.com/CherryHQ/cherry-studio/compare/v1.9.6...v1.9.7</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>quase só correções e hotfixes</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8100,8 +9936,11 @@
           <t>https://github.com/CherryHQ/cherry-studio/compare/v2.0.2...v2.0.3</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8129,8 +9968,16 @@
           <t>https://github.com/modelcontextprotocol/kotlin-sdk/compare/0.7.2...0.6.1</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>uma correção de desserialização</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8158,8 +10005,11 @@
           <t>https://github.com/modelcontextprotocol/kotlin-sdk/compare/0.6.1...0.7.3</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8187,8 +10037,16 @@
           <t>https://github.com/modelcontextprotocol/kotlin-sdk/compare/0.7.4...0.7.5</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>correções misturadas com refatorações e campo _meta novo</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8216,8 +10074,16 @@
           <t>https://github.com/modelcontextprotocol/kotlin-sdk/compare/0.7.6...0.7.7</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>mudança de tipo com quebra de compatibilidade, sem defeito descrito</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8245,8 +10111,16 @@
           <t>https://github.com/modelcontextprotocol/kotlin-sdk/compare/0.8.1...0.8.3</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>seção Bugfixes domina; uma funcionalidade pequena</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8274,8 +10148,16 @@
           <t>https://github.com/valkey-io/valkey/compare/8.0.5...7.2.11</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>release de segurança (CVEs no Lua) e correções</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8303,8 +10185,16 @@
           <t>https://github.com/valkey-io/valkey/compare/7.2.12...8.0.7</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>release de segurança e correções</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8332,8 +10222,16 @@
           <t>https://github.com/valkey-io/valkey/compare/8.0.7...8.1.6</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>release de segurança e correções</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8361,8 +10259,16 @@
           <t>https://github.com/valkey-io/valkey/compare/8.1.7...8.0.8</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>release revogada; notas não descrevem conteúdo</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8390,8 +10296,16 @@
           <t>https://github.com/valkey-io/valkey/compare/8.1.9...9.0.5</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>release de segurança e correções</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8419,8 +10333,16 @@
           <t>https://github.com/apollographql/apollo-client/compare/%40apollo%2Fclient%404.1.5...%40apollo%2Fclient%404.1.6</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>corrige mismatch de hidratação</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8448,8 +10370,16 @@
           <t>https://github.com/apollographql/apollo-client/compare/%40apollo%2Fclient%404.1.7...%40apollo%2Fclient%404.1.8</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>adiciona skill para agentes</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8477,8 +10407,16 @@
           <t>https://github.com/apollographql/apollo-client/compare/%40apollo%2Fclient-graphql-codegen%402.1.1...%40apollo%2Fclient%404.2.6</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>corrige fetch após falha de serialização e detecção errada de @stream</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8506,8 +10444,16 @@
           <t>https://github.com/apollographql/apollo-client/compare/%40apollo%2Fclient%404.2.9...%40apollo%2Fclient%404.2.10</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>correções de tipos</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8535,8 +10481,16 @@
           <t>https://github.com/apollographql/apollo-client/compare/%40apollo%2Fclient%404.3.0...%40apollo%2Fclient%404.3.1</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>corrige rerender do useLazyQuery</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8564,8 +10518,16 @@
           <t>https://github.com/vuetifyjs/vuetify/compare/v3.10.3...v3.10.4</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>maioria correções; duas funcionalidades pequenas (prop always-filter, zoom CSS)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8593,8 +10555,16 @@
           <t>https://github.com/vuetifyjs/vuetify/compare/v3.10.8...v3.10.9</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>só Bug Fixes</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8622,8 +10592,16 @@
           <t>https://github.com/vuetifyjs/vuetify/compare/v3.12.10...v4.1.5</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>só Bug Fixes</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8651,8 +10629,16 @@
           <t>https://github.com/vuetifyjs/vuetify/compare/v4.1.9...v3.13.2</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>duas correções</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8680,8 +10666,11 @@
           <t>https://github.com/vuetifyjs/vuetify/compare/v4.1.13...v4.2.0</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8709,8 +10698,16 @@
           <t>https://github.com/rilldata/rill/compare/v0.81.1...v0.81.2</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>três correções e ajuste de build</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8738,8 +10735,16 @@
           <t>https://github.com/rilldata/rill/compare/v0.83.1...v0.83.2</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>aumento de limite de mensagem, sem defeito descrito</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8767,8 +10772,16 @@
           <t>https://github.com/rilldata/rill/compare/v0.84.3...v0.84.4</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>corrige race no carregamento do dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8796,8 +10809,11 @@
           <t>https://github.com/rilldata/rill/compare/v0.84.4...v0.85.0</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8825,8 +10841,16 @@
           <t>https://github.com/rilldata/rill/compare/v0.87.5...v0.87.6</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>reverte funcionalidade, mas também adiciona dimensões de tempo nos seletores</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8854,8 +10878,16 @@
           <t>https://github.com/posit-dev/great-tables/compare/v0.18.0...v0.19.0</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>correções junto com remoção do NumPy e novos padrões de alinhamento</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8883,8 +10915,11 @@
           <t>https://github.com/posit-dev/great-tables/compare/v0.19.0...v0.20.0</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8912,8 +10947,11 @@
           <t>https://github.com/posit-dev/great-tables/compare/v0.20.0...v0.21.0</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8941,8 +10979,11 @@
           <t>https://github.com/posit-dev/great-tables/compare/v0.22.0...v0.23.0</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8970,8 +11011,11 @@
           <t>https://github.com/posit-dev/great-tables/compare/v0.23.0...v0.24.0</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8999,8 +11043,11 @@
           <t>https://github.com/vstorm-co/full-stack-ai-agent-template/compare/0.1.3...0.1.4</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9028,8 +11075,16 @@
           <t>https://github.com/vstorm-co/full-stack-ai-agent-template/compare/0.1.7...0.1.8</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>só documentação e versão</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9057,8 +11112,16 @@
           <t>https://github.com/vstorm-co/full-stack-ai-agent-template/compare/0.1.11...0.1.11-fix</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>republicação da 0.1.11 para corrigir a versão da lib</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9086,8 +11149,11 @@
           <t>https://github.com/vstorm-co/full-stack-ai-agent-template/compare/0.2.2...0.2.3</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9115,8 +11181,16 @@
           <t>https://github.com/vstorm-co/full-stack-ai-agent-template/compare/0.2.3...0.2.4</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>correção de segurança (SSRF)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9144,8 +11218,16 @@
           <t>https://github.com/aaif-goose/goose/compare/v1.9.1...v1.9.2</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>patch de release branch dominado por correções</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9173,8 +11255,16 @@
           <t>https://github.com/aaif-goose/goose/compare/v1.10.1...v1.10.2</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>corrige ausência do build Apple Silicon</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9202,8 +11292,11 @@
           <t>https://github.com/aaif-goose/goose/compare/v1.17.0...v1.18.0</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9231,8 +11324,16 @@
           <t>https://github.com/aaif-goose/goose/compare/v1.22.1...v1.22.2</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>corrige release quebrada</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9260,8 +11361,16 @@
           <t>https://github.com/aaif-goose/goose/compare/v1.43.0...v1.44.0</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>correção de segurança junto com várias funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9289,8 +11398,16 @@
           <t>https://github.com/awalol/DS5Dongle/commits/v0.1</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>primeira release</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9318,8 +11435,16 @@
           <t>https://github.com/awalol/DS5Dongle/compare/v0.5.0...v0.3.3</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>uma funcionalidade e uma correção</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9347,8 +11472,16 @@
           <t>https://github.com/awalol/DS5Dongle/compare/v0.5.3...v0.5.4</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>correções junto com watchdog novo</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9376,8 +11509,16 @@
           <t>https://github.com/awalol/DS5Dongle/compare/v0.6.0...v0.6.0-hotfix</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>hotfix do rumble</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9405,8 +11546,16 @@
           <t>https://github.com/awalol/DS5Dongle/compare/v0.7.0...v0.7.1</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>reverte commit que quebrou a configuração web</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9434,8 +11583,11 @@
           <t>https://github.com/mock-server/mockserver-monorepo/commits/mockserver-6.0.0</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9463,8 +11615,16 @@
           <t>https://github.com/mock-server/mockserver-monorepo/compare/mockserver-6.0.0...mockserver-6.1.0</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>notas vazias; commits corrigem o pipeline de publicação da 6.0.0 e o empacotamento do SLF4J</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9492,8 +11652,11 @@
           <t>https://github.com/mock-server/mockserver-monorepo/compare/mockserver-7.2.0...mockserver-7.3.0</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9521,8 +11684,16 @@
           <t>https://github.com/mock-server/mockserver-monorepo/compare/mockserver-7.4.0...mockserver-7.5.0</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>correção de segurança em destaque, mas também 3 Added e 13 Changed</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9550,8 +11721,11 @@
           <t>https://github.com/mock-server/mockserver-monorepo/compare/mockserver-7.5.0...mockserver-7.6.0</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9579,8 +11753,16 @@
           <t>https://github.com/rmyndharis/OpenWA/compare/v0.1.5...v0.1.6</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>única mudança funcional é a correção da migração no PostgreSQL; resto é dependência</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9608,8 +11790,16 @@
           <t>https://github.com/rmyndharis/OpenWA/compare/v0.2.2...v0.2.3</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>patch que corrige o dashboard em HTTP fora de localhost</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9637,8 +11827,11 @@
           <t>https://github.com/rmyndharis/OpenWA/compare/v0.7.8...v0.7.9</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9666,8 +11859,16 @@
           <t>https://github.com/rmyndharis/OpenWA/compare/v0.7.10...v0.7.11</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>muitas correções, mas destaca suporte a mensagens temporárias</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9695,8 +11896,16 @@
           <t>https://github.com/rmyndharis/OpenWA/compare/v0.7.19...v0.7.20</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>corrige falhas de envio para contatos LID</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9724,8 +11933,11 @@
           <t>https://github.com/phpactor/phpactor/compare/2025.07.25.0...2025.10.17.0</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9753,8 +11965,11 @@
           <t>https://github.com/phpactor/phpactor/compare/2025.10.17.0...2025.12.21.0</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9782,8 +11997,16 @@
           <t>https://github.com/phpactor/phpactor/compare/2026.05.30.1...2026.05.30.2</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>uma correção</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9811,8 +12034,16 @@
           <t>https://github.com/phpactor/phpactor/compare/2026.06.25.0...2026.07.22.0</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>nova code action além das correções</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9840,8 +12071,16 @@
           <t>https://github.com/phpactor/phpactor/compare/2026.07.22.0...2026.06.23.0</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>duas melhorias e duas correções</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9869,8 +12108,16 @@
           <t>https://github.com/coredevices/PebbleOS/compare/v4.9.74...v4.9.75</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>sem notas; commit só desativa o memfault numa variante</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9898,8 +12145,16 @@
           <t>https://github.com/coredevices/PebbleOS/compare/v4.9.123...v4.9.124</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>sem notas; reverte dois commits e corrige crash</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9927,8 +12182,16 @@
           <t>https://github.com/coredevices/PebbleOS/compare/v4.9.134...v4.9.135</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>sem notas; commit só adiciona logs</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9956,8 +12219,16 @@
           <t>https://github.com/coredevices/PebbleOS/compare/v4.9.136...v4.9.137</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>sem notas; correções no HRM junto com funcionalidade nova</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9985,8 +12256,16 @@
           <t>https://github.com/coredevices/PebbleOS/compare/v4.9.172...v4.9.173</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>sem notas; adiciona mute do alto-falante</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10014,8 +12293,11 @@
           <t>https://github.com/zeroclaw-labs/zeroclaw/compare/v0.1.6...v0.1.7</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10043,8 +12325,16 @@
           <t>https://github.com/zeroclaw-labs/zeroclaw/compare/v0.5.0...v0.5.1</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>notas listam só funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10072,8 +12362,11 @@
           <t>https://github.com/zeroclaw-labs/zeroclaw/compare/v0.6.9...v0.7.3</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10101,8 +12394,11 @@
           <t>https://github.com/zeroclaw-labs/zeroclaw/compare/v0.7.5...v0.8.0</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10130,8 +12426,11 @@
           <t>https://github.com/zeroclaw-labs/zeroclaw/compare/v0.8.2...v0.8.3</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10159,8 +12458,16 @@
           <t>https://github.com/mozilla/rhino/compare/Rhino1_8_0_Release...Rhino1_8_1_Release</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>corrige problema de desempenho na formatação de números</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10188,8 +12495,16 @@
           <t>https://github.com/mozilla/rhino/compare/Rhino1_8_1_Release...Rhino1_7_15_1_Release</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>mesmo conserto portado para a 1.7.15</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10217,8 +12532,16 @@
           <t>https://github.com/mozilla/rhino/compare/Rhino1_7_15_1_Release...Rhino1_7_14_1_Release</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>mesmo conserto portado para a 1.7.14</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10246,8 +12569,11 @@
           <t>https://github.com/mozilla/rhino/compare/Rhino1_7_14_1_Release...Rhino1_9_0_Release</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10275,8 +12601,16 @@
           <t>https://github.com/mozilla/rhino/compare/Rhino1_9_0_Release...Rhino1_9_1_Release</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>corrige regressões da 1.9.0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
